--- a/psychopy_exp_files/sequences/learning_block4_fixed-middle-10_50.xlsx
+++ b/psychopy_exp_files/sequences/learning_block4_fixed-middle-10_50.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_09.jpg</t>
+          <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>13</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W2" t="n">
         <v>17</v>
@@ -668,12 +668,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_02.jpg</t>
+          <t>stimuli/ball/ball_09.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
+          <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -734,10 +734,10 @@
         <v>13</v>
       </c>
       <c r="U3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W3" t="n">
         <v>14</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_02.jpg</t>
+          <t>stimuli/ball/ball_09.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -830,7 +830,7 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
         <v>2</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/dog/dog_39.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -935,7 +935,7 @@
         <v>8</v>
       </c>
       <c r="V5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W5" t="n">
         <v>14</v>
@@ -965,12 +965,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_09.jpg</t>
+          <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1031,10 +1031,10 @@
         <v>8</v>
       </c>
       <c r="U6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W6" t="n">
         <v>7</v>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_09.jpg</t>
+          <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1127,10 +1127,10 @@
         <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V7" t="n">
         <v>16</v>
@@ -1158,17 +1158,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_09.jpg</t>
+          <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/dog/dog_39.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_46.jpg</t>
+          <t>stimuli/jacket/jacket_49.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1178,17 +1178,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1226,13 +1226,13 @@
         <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
         <v>17</v>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/dog/dog_39.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_46.jpg</t>
+          <t>stimuli/jacket/jacket_49.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1325,10 +1325,10 @@
         <v>9</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V9" t="n">
         <v>14</v>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_46.jpg</t>
+          <t>stimuli/jacket/jacket_49.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
+          <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1424,10 +1424,10 @@
         <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="V10" t="n">
         <v>7</v>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
+          <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_02.jpg</t>
+          <t>stimuli/ball/ball_09.jpg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1523,7 +1523,7 @@
         <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
         <v>7</v>
@@ -1532,7 +1532,7 @@
         <v>16</v>
       </c>
       <c r="W11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1631,7 +1631,7 @@
         <v>13</v>
       </c>
       <c r="W12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/dog/dog_39.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1730,7 +1730,7 @@
         <v>16</v>
       </c>
       <c r="W13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1826,7 +1826,7 @@
         <v>17</v>
       </c>
       <c r="V14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W14" t="n">
         <v>16</v>
@@ -1960,12 +1960,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_34.jpg</t>
+          <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2024,10 +2024,10 @@
         <v>9</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/bread/bread_30.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2123,7 +2123,7 @@
         <v>8</v>
       </c>
       <c r="V17" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W17" t="n">
         <v>15</v>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2318,7 +2318,7 @@
         <v>7</v>
       </c>
       <c r="U19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V19" t="n">
         <v>12</v>
@@ -2346,17 +2346,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_38.jpg</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_06.jpg</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/ball/ball_34.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2366,17 +2366,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2414,13 +2414,13 @@
         <v>7</v>
       </c>
       <c r="T20" t="n">
+        <v>10</v>
+      </c>
+      <c r="U20" t="n">
         <v>6</v>
       </c>
-      <c r="U20" t="n">
-        <v>5</v>
-      </c>
       <c r="V20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W20" t="n">
         <v>13</v>
@@ -2445,42 +2445,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_30.jpg</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_30.jpg</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_06.jpg</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_30.jpg</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_30.jpg</t>
-        </is>
-      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_34.jpg</t>
+          <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2513,16 +2513,16 @@
         <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U21" t="n">
         <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/bread/bread_30.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2615,7 +2615,7 @@
         <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="V22" t="n">
         <v>15</v>
@@ -2643,12 +2643,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/bread/bread_30.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_30.jpg</t>
+          <t>stimuli/dog/dog_06.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2658,17 +2658,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_06.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2711,16 +2711,16 @@
         <v>10</v>
       </c>
       <c r="T23" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V23" t="n">
         <v>13</v>
       </c>
       <c r="W23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_30.jpg</t>
+          <t>stimuli/dog/dog_06.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/ball/ball_34.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2757,17 +2757,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2810,16 +2810,16 @@
         <v>11</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V24" t="n">
         <v>14</v>
       </c>
       <c r="W24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_34.jpg</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_34.jpg</t>
-        </is>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>stimuli/fish/fish_40.jpg</t>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>ball</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2909,10 +2909,10 @@
         <v>12</v>
       </c>
       <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
         <v>4</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1</v>
       </c>
       <c r="V25" t="n">
         <v>12</v>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_34.jpg</t>
+          <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3008,7 +3008,7 @@
         <v>13</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U26" t="n">
         <v>15</v>
@@ -3017,7 +3017,7 @@
         <v>9</v>
       </c>
       <c r="W26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_02.jpg</t>
+          <t>stimuli/ball/ball_09.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3212,7 +3212,7 @@
         <v>13</v>
       </c>
       <c r="V28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W28" t="n">
         <v>17</v>
@@ -3242,12 +3242,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_02.jpg</t>
+          <t>stimuli/ball/ball_09.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3308,10 +3308,10 @@
         <v>13</v>
       </c>
       <c r="U29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W29" t="n">
         <v>14</v>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_02.jpg</t>
+          <t>stimuli/ball/ball_09.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/dog/dog_39.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3404,13 +3404,13 @@
         <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
         <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W30" t="n">
         <v>17</v>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3509,7 +3509,7 @@
         <v>8</v>
       </c>
       <c r="V31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W31" t="n">
         <v>9</v>
@@ -3539,12 +3539,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_46.jpg</t>
+          <t>stimuli/jacket/jacket_49.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3605,10 +3605,10 @@
         <v>8</v>
       </c>
       <c r="U32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V32" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W32" t="n">
         <v>14</v>
@@ -3633,19 +3633,19 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_46.jpg</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_02.jpg</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_39.jpg</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_09.jpg</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_38.jpg</t>
-        </is>
-      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>stimuli/hammer/hammer_46.jpg</t>
@@ -3653,17 +3653,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3701,13 +3701,13 @@
         <v>7</v>
       </c>
       <c r="T33" t="n">
+        <v>6</v>
+      </c>
+      <c r="U33" t="n">
+        <v>4</v>
+      </c>
+      <c r="V33" t="n">
         <v>5</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1</v>
-      </c>
-      <c r="V33" t="n">
-        <v>3</v>
       </c>
       <c r="W33" t="n">
         <v>7</v>
@@ -3732,19 +3732,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_09.jpg</t>
+          <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_39.jpg</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
-        </is>
-      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>stimuli/lamp/lamp_24.jpg</t>
@@ -3752,17 +3752,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3800,13 +3800,13 @@
         <v>8</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U34" t="n">
+        <v>5</v>
+      </c>
+      <c r="V34" t="n">
         <v>3</v>
-      </c>
-      <c r="V34" t="n">
-        <v>10</v>
       </c>
       <c r="W34" t="n">
         <v>14</v>
@@ -3831,12 +3831,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/dog/dog_39.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_46.jpg</t>
+          <t>stimuli/jacket/jacket_49.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3899,10 +3899,10 @@
         <v>9</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U35" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V35" t="n">
         <v>17</v>
@@ -3930,12 +3930,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_46.jpg</t>
+          <t>stimuli/jacket/jacket_49.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
+          <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3945,17 +3945,17 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_09.jpg</t>
+          <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3998,16 +3998,16 @@
         <v>10</v>
       </c>
       <c r="T36" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U36" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="V36" t="n">
         <v>8</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
+          <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/dog/dog_39.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4097,7 +4097,7 @@
         <v>11</v>
       </c>
       <c r="T37" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
         <v>7</v>
@@ -4106,7 +4106,7 @@
         <v>16</v>
       </c>
       <c r="W37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_46.jpg</t>
+          <t>stimuli/jacket/jacket_49.jpg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4205,7 +4205,7 @@
         <v>2</v>
       </c>
       <c r="W38" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
@@ -4237,14 +4237,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_46.jpg</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_39.jpg</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_38.jpg</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>house</t>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4301,10 +4301,10 @@
         <v>14</v>
       </c>
       <c r="V39" t="n">
+        <v>6</v>
+      </c>
+      <c r="W39" t="n">
         <v>5</v>
-      </c>
-      <c r="W39" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/bread/bread_30.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4499,7 +4499,7 @@
         <v>14</v>
       </c>
       <c r="V41" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W41" t="n">
         <v>13</v>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/ball/ball_34.jpg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4601,7 +4601,7 @@
         <v>7</v>
       </c>
       <c r="W42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_30.jpg</t>
+          <t>stimuli/dog/dog_06.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4697,7 +4697,7 @@
         <v>8</v>
       </c>
       <c r="V43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W43" t="n">
         <v>15</v>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_34.jpg</t>
+          <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4796,7 +4796,7 @@
         <v>7</v>
       </c>
       <c r="V44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W44" t="n">
         <v>13</v>
@@ -4826,14 +4826,14 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_38.jpg</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_06.jpg</t>
-        </is>
-      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>stimuli/key/key_35.jpg</t>
@@ -4846,12 +4846,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>dog</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4892,10 +4892,10 @@
         <v>7</v>
       </c>
       <c r="U45" t="n">
+        <v>10</v>
+      </c>
+      <c r="V45" t="n">
         <v>6</v>
-      </c>
-      <c r="V45" t="n">
-        <v>5</v>
       </c>
       <c r="W45" t="n">
         <v>15</v>
@@ -4920,14 +4920,14 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_38.jpg</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_06.jpg</t>
-        </is>
-      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>stimuli/fish/fish_40.jpg</t>
@@ -4940,12 +4940,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>dog</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4988,10 +4988,10 @@
         <v>7</v>
       </c>
       <c r="T46" t="n">
+        <v>10</v>
+      </c>
+      <c r="U46" t="n">
         <v>6</v>
-      </c>
-      <c r="U46" t="n">
-        <v>5</v>
       </c>
       <c r="V46" t="n">
         <v>12</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_06.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5087,7 +5087,7 @@
         <v>8</v>
       </c>
       <c r="T47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U47" t="n">
         <v>2</v>
@@ -5123,19 +5123,19 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_30.jpg</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_06.jpg</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_30.jpg</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_30.jpg</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>bicycle</t>
@@ -5143,17 +5143,17 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t>jacket</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5189,13 +5189,13 @@
         <v>2</v>
       </c>
       <c r="U48" t="n">
+        <v>3</v>
+      </c>
+      <c r="V48" t="n">
+        <v>5</v>
+      </c>
+      <c r="W48" t="n">
         <v>10</v>
-      </c>
-      <c r="V48" t="n">
-        <v>3</v>
-      </c>
-      <c r="W48" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="49">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/bread/bread_30.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_30.jpg</t>
+          <t>stimuli/dog/dog_06.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5285,10 +5285,10 @@
         <v>10</v>
       </c>
       <c r="T49" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V49" t="n">
         <v>9</v>
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_30.jpg</t>
+          <t>stimuli/dog/dog_06.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/ball/ball_34.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5384,10 +5384,10 @@
         <v>11</v>
       </c>
       <c r="T50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V50" t="n">
         <v>15</v>
@@ -5415,14 +5415,14 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_34.jpg</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_34.jpg</t>
-        </is>
-      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>stimuli/fish/fish_40.jpg</t>
@@ -5435,12 +5435,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>ball</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5483,10 +5483,10 @@
         <v>12</v>
       </c>
       <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
         <v>4</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1</v>
       </c>
       <c r="V51" t="n">
         <v>12</v>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_34.jpg</t>
+          <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5529,12 +5529,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_30.jpg</t>
+          <t>stimuli/dog/dog_06.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5582,7 +5582,7 @@
         <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U52" t="n">
         <v>15</v>
@@ -5591,7 +5591,7 @@
         <v>14</v>
       </c>
       <c r="W52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
+          <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5786,7 +5786,7 @@
         <v>13</v>
       </c>
       <c r="V54" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W54" t="n">
         <v>17</v>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_02.jpg</t>
+          <t>stimuli/ball/ball_09.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5882,7 +5882,7 @@
         <v>13</v>
       </c>
       <c r="U55" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V55" t="n">
         <v>8</v>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_02.jpg</t>
+          <t>stimuli/ball/ball_09.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_46.jpg</t>
+          <t>stimuli/jacket/jacket_49.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5978,13 +5978,13 @@
         <v>4</v>
       </c>
       <c r="T56" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U56" t="n">
         <v>2</v>
       </c>
       <c r="V56" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W56" t="n">
         <v>17</v>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
+          <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6083,7 +6083,7 @@
         <v>8</v>
       </c>
       <c r="V57" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W57" t="n">
         <v>14</v>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_09.jpg</t>
+          <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6179,10 +6179,10 @@
         <v>8</v>
       </c>
       <c r="U58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V58" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W58" t="n">
         <v>17</v>
@@ -6207,12 +6207,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_09.jpg</t>
+          <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -6275,10 +6275,10 @@
         <v>7</v>
       </c>
       <c r="T59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U59" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V59" t="n">
         <v>7</v>
@@ -6306,12 +6306,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_09.jpg</t>
+          <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/dog/dog_39.jpg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6374,10 +6374,10 @@
         <v>8</v>
       </c>
       <c r="T60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V60" t="n">
         <v>14</v>
@@ -6405,12 +6405,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/dog/dog_39.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_46.jpg</t>
+          <t>stimuli/jacket/jacket_49.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -6425,12 +6425,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6473,10 +6473,10 @@
         <v>9</v>
       </c>
       <c r="T61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U61" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V61" t="n">
         <v>9</v>
@@ -6504,42 +6504,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_49.jpg</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_38.jpg</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>stimuli/pencil/pencil_13.jpg</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>stimuli/pencil/pencil_13.jpg</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_39.jpg</t>
-        </is>
-      </c>
       <c r="I62" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>pencil</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>pencil</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>dog</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6572,16 +6572,16 @@
         <v>10</v>
       </c>
       <c r="T62" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U62" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="V62" t="n">
         <v>16</v>
       </c>
       <c r="W62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
+          <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/dog/dog_39.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6671,7 +6671,7 @@
         <v>11</v>
       </c>
       <c r="T63" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U63" t="n">
         <v>7</v>
@@ -6680,7 +6680,7 @@
         <v>14</v>
       </c>
       <c r="W63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_02.jpg</t>
+          <t>stimuli/ball/ball_09.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6776,10 +6776,10 @@
         <v>9</v>
       </c>
       <c r="V64" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_09.jpg</t>
+          <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6878,7 +6878,7 @@
         <v>16</v>
       </c>
       <c r="W65" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/dog/dog_39.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6974,7 +6974,7 @@
         <v>17</v>
       </c>
       <c r="V66" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W66" t="n">
         <v>16</v>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/ball/ball_34.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7073,7 +7073,7 @@
         <v>14</v>
       </c>
       <c r="V67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W67" t="n">
         <v>13</v>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/bread/bread_30.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7172,7 +7172,7 @@
         <v>9</v>
       </c>
       <c r="V68" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W68" t="n">
         <v>15</v>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7271,7 +7271,7 @@
         <v>8</v>
       </c>
       <c r="V69" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W69" t="n">
         <v>13</v>
@@ -7400,17 +7400,17 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/bread/bread_30.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_34.jpg</t>
+          <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7420,17 +7420,17 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7466,13 +7466,13 @@
         <v>7</v>
       </c>
       <c r="U71" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V71" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W71" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
@@ -7494,42 +7494,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_38.jpg</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_30.jpg</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
         <is>
           <t>stimuli/dog/dog_06.jpg</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_30.jpg</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_30.jpg</t>
-        </is>
-      </c>
       <c r="I72" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7562,16 +7562,16 @@
         <v>7</v>
       </c>
       <c r="T72" t="n">
+        <v>10</v>
+      </c>
+      <c r="U72" t="n">
         <v>6</v>
-      </c>
-      <c r="U72" t="n">
-        <v>5</v>
       </c>
       <c r="V72" t="n">
         <v>2</v>
       </c>
       <c r="W72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_06.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7661,7 +7661,7 @@
         <v>8</v>
       </c>
       <c r="T73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U73" t="n">
         <v>2</v>
@@ -7697,12 +7697,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/bread/bread_30.jpg</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_34.jpg</t>
+          <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7763,10 +7763,10 @@
         <v>2</v>
       </c>
       <c r="U74" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="V74" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W74" t="n">
         <v>7</v>
@@ -7791,42 +7791,42 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_30.jpg</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_06.jpg</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_44.jpg</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_30.jpg</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_44.jpg</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_30.jpg</t>
-        </is>
-      </c>
       <c r="I75" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
           <t>jacket</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7859,16 +7859,16 @@
         <v>10</v>
       </c>
       <c r="T75" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U75" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V75" t="n">
         <v>9</v>
       </c>
       <c r="W75" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76">
@@ -7890,12 +7890,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_30.jpg</t>
+          <t>stimuli/dog/dog_06.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/ball/ball_34.jpg</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -7905,17 +7905,17 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_06.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7958,16 +7958,16 @@
         <v>11</v>
       </c>
       <c r="T76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U76" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V76" t="n">
         <v>12</v>
       </c>
       <c r="W76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
@@ -7989,14 +7989,14 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_34.jpg</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_34.jpg</t>
-        </is>
-      </c>
       <c r="G77" t="inlineStr">
         <is>
           <t>stimuli/lamp/lamp_01.jpg</t>
@@ -8004,19 +8004,19 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>lamp</t>
@@ -8024,7 +8024,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8057,16 +8057,16 @@
         <v>12</v>
       </c>
       <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
         <v>4</v>
-      </c>
-      <c r="U77" t="n">
-        <v>1</v>
       </c>
       <c r="V77" t="n">
         <v>14</v>
       </c>
       <c r="W77" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_34.jpg</t>
+          <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8156,7 +8156,7 @@
         <v>13</v>
       </c>
       <c r="T78" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U78" t="n">
         <v>15</v>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_02.jpg</t>
+          <t>stimuli/ball/ball_09.jpg</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -8456,7 +8456,7 @@
         <v>13</v>
       </c>
       <c r="U81" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V81" t="n">
         <v>2</v>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_02.jpg</t>
+          <t>stimuli/ball/ball_09.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -8552,7 +8552,7 @@
         <v>4</v>
       </c>
       <c r="T82" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U82" t="n">
         <v>2</v>
@@ -8593,7 +8593,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_46.jpg</t>
+          <t>stimuli/jacket/jacket_49.jpg</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8657,7 +8657,7 @@
         <v>8</v>
       </c>
       <c r="V83" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W83" t="n">
         <v>14</v>
@@ -8687,7 +8687,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_02.jpg</t>
+          <t>stimuli/ball/ball_09.jpg</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8753,13 +8753,13 @@
         <v>8</v>
       </c>
       <c r="U84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V84" t="n">
         <v>16</v>
       </c>
       <c r="W84" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_09.jpg</t>
+          <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -8849,10 +8849,10 @@
         <v>7</v>
       </c>
       <c r="T85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U85" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V85" t="n">
         <v>13</v>
@@ -8880,19 +8880,19 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_09.jpg</t>
+          <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_39.jpg</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
-        </is>
-      </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>stimuli/phone/phone_34.jpg</t>
@@ -8900,17 +8900,17 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8948,13 +8948,13 @@
         <v>8</v>
       </c>
       <c r="T86" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U86" t="n">
+        <v>5</v>
+      </c>
+      <c r="V86" t="n">
         <v>3</v>
-      </c>
-      <c r="V86" t="n">
-        <v>10</v>
       </c>
       <c r="W86" t="n">
         <v>17</v>
@@ -8979,42 +8979,42 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/dog/dog_39.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_49.jpg</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_24.jpg</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>stimuli/lamp/lamp_24.jpg</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_39.jpg</t>
-        </is>
-      </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>dog</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9047,16 +9047,16 @@
         <v>9</v>
       </c>
       <c r="T87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U87" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V87" t="n">
         <v>14</v>
       </c>
       <c r="W87" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88">
@@ -9078,12 +9078,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_46.jpg</t>
+          <t>stimuli/jacket/jacket_49.jpg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
+          <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -9093,17 +9093,17 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_09.jpg</t>
+          <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9146,16 +9146,16 @@
         <v>10</v>
       </c>
       <c r="T88" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U88" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="V88" t="n">
         <v>17</v>
       </c>
       <c r="W88" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
+          <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_02.jpg</t>
+          <t>stimuli/ball/ball_09.jpg</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -9245,13 +9245,13 @@
         <v>11</v>
       </c>
       <c r="T89" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U89" t="n">
         <v>7</v>
       </c>
       <c r="V89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W89" t="n">
         <v>8</v>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/dog/dog_39.jpg</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -9353,7 +9353,7 @@
         <v>14</v>
       </c>
       <c r="W90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9746,7 +9746,7 @@
         <v>9</v>
       </c>
       <c r="V94" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W94" t="n">
         <v>13</v>
@@ -9781,12 +9781,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_30.jpg</t>
+          <t>stimuli/dog/dog_06.jpg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_34.jpg</t>
+          <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -9845,10 +9845,10 @@
         <v>8</v>
       </c>
       <c r="V95" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_06.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -9900,7 +9900,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9944,7 +9944,7 @@
         <v>7</v>
       </c>
       <c r="V96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W96" t="n">
         <v>12</v>
@@ -9974,12 +9974,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/ball/ball_34.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -10040,10 +10040,10 @@
         <v>7</v>
       </c>
       <c r="U97" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V97" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W97" t="n">
         <v>13</v>
@@ -10068,14 +10068,14 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_38.jpg</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_06.jpg</t>
-        </is>
-      </c>
       <c r="G98" t="inlineStr">
         <is>
           <t>stimuli/bicycle/bicycle_30.jpg</t>
@@ -10083,19 +10083,19 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_34.jpg</t>
+          <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>bicycle</t>
@@ -10103,7 +10103,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -10136,16 +10136,16 @@
         <v>7</v>
       </c>
       <c r="T98" t="n">
+        <v>10</v>
+      </c>
+      <c r="U98" t="n">
         <v>6</v>
-      </c>
-      <c r="U98" t="n">
-        <v>5</v>
       </c>
       <c r="V98" t="n">
         <v>2</v>
       </c>
       <c r="W98" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_06.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -10235,7 +10235,7 @@
         <v>8</v>
       </c>
       <c r="T99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U99" t="n">
         <v>2</v>
@@ -10271,12 +10271,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/bread/bread_30.jpg</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_34.jpg</t>
+          <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -10337,10 +10337,10 @@
         <v>2</v>
       </c>
       <c r="U100" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="V100" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W100" t="n">
         <v>9</v>
@@ -10365,12 +10365,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/bread/bread_30.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_30.jpg</t>
+          <t>stimuli/dog/dog_06.jpg</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -10433,10 +10433,10 @@
         <v>10</v>
       </c>
       <c r="T101" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U101" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V101" t="n">
         <v>12</v>
@@ -10464,12 +10464,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_30.jpg</t>
+          <t>stimuli/dog/dog_06.jpg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/ball/ball_34.jpg</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -10479,17 +10479,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -10532,16 +10532,16 @@
         <v>11</v>
       </c>
       <c r="T102" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U102" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V102" t="n">
         <v>13</v>
       </c>
       <c r="W102" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103">
@@ -10563,14 +10563,14 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_34.jpg</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_34.jpg</t>
-        </is>
-      </c>
       <c r="G103" t="inlineStr">
         <is>
           <t>stimuli/hand/hand_25.jpg</t>
@@ -10578,19 +10578,19 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/bread/bread_30.jpg</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="K103" t="inlineStr">
         <is>
           <t>hand</t>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -10631,16 +10631,16 @@
         <v>12</v>
       </c>
       <c r="T103" t="n">
+        <v>1</v>
+      </c>
+      <c r="U103" t="n">
         <v>4</v>
-      </c>
-      <c r="U103" t="n">
-        <v>1</v>
       </c>
       <c r="V103" t="n">
         <v>8</v>
       </c>
       <c r="W103" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_34.jpg</t>
+          <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -10730,7 +10730,7 @@
         <v>13</v>
       </c>
       <c r="T104" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U104" t="n">
         <v>15</v>
@@ -10776,7 +10776,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_30.jpg</t>
+          <t>stimuli/dog/dog_06.jpg</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -10838,7 +10838,7 @@
         <v>7</v>
       </c>
       <c r="W105" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
